--- a/survey_templates/038_previous_year_party_survey_form--survey_templates.xlsx
+++ b/survey_templates/038_previous_year_party_survey_form--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="43" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,17 +515,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>previous_year_party</t>
+          <t>party_theme</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>previous_year_party</t>
+          <t>What was the party theme?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,7 +538,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>party_prophets</t>
+          <t>Who was a prophet at the party?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>party_theme</t>
+          <t>party_attendees</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>party_theme</t>
+          <t>How many people attended the party?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>party_venue</t>
+          <t>Where was the party held?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>party_food</t>
+          <t>What type of food was served?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>party_dress</t>
+          <t>What was the dress code for the party?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>party_entertainment</t>
+          <t>What type of entertainment was provided?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>party_cost</t>
+          <t>How much did the party cost?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>party_comments</t>
+          <t>Do you have any comments about the party?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>party_planner_name</t>
+          <t>What is your name?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>party_prophets</t>
+          <t>party_prophets_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>party_prophets</t>
+          <t>Was there a prophet at the party?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,131 +773,16 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>party_planners</t>
+          <t>party_prophets2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>party_planners</t>
+          <t>Was there a second prophet at the party?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>party_prophets</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>party_prophets</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>party_prophets</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>party_prophets</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>party_prophets</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>party_prophets</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>party_planners</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>party_planners</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>party_prophets</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>party_prophets</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -914,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -942,391 +827,306 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>party_prophets_choices</t>
+          <t>party_theme_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>theme1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Theme1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>party_prophets_choices</t>
+          <t>party_theme_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>theme2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Theme2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>party_venue_choices</t>
+          <t>party_theme_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'venue1'}</t>
+          <t>theme3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Venue1'}</t>
+          <t>Theme3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>party_venue_choices</t>
+          <t>party_prophets_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>prophet1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Prophet1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>party_food_choices</t>
+          <t>party_prophets_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'food1'}</t>
+          <t>prophet2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Food1'}</t>
+          <t>Prophet2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>party_food_choices</t>
+          <t>party_prophets_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'food2'}</t>
+          <t>prophet3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Food2'}</t>
+          <t>Prophet3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>party_food_choices</t>
+          <t>party_venue_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'food3'}</t>
+          <t>venue1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Food3'}</t>
+          <t>Venue1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>party_dress_choices</t>
+          <t>party_venue_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'dress1'}</t>
+          <t>venue2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Dress1'}</t>
+          <t>Venue2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>party_dress_choices</t>
+          <t>party_venue_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'dress2'}</t>
+          <t>venue3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Dress2'}</t>
+          <t>Venue3</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>party_dress_choices</t>
+          <t>party_food_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'dress3'}</t>
+          <t>food1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Dress3'}</t>
+          <t>Food1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>party_entertainment_choices</t>
+          <t>party_food_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'entertainment1'}</t>
+          <t>food2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Entertainment1'}</t>
+          <t>Food2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>party_entertainment_choices</t>
+          <t>party_food_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'entertainment2'}</t>
+          <t>food3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Entertainment2'}</t>
+          <t>Food3</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>party_entertainment_choices</t>
+          <t>party_dress_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'entertainment3'}</t>
+          <t>dress1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Entertainment3'}</t>
+          <t>Dress1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>party_prophets_choices</t>
+          <t>party_dress_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'prophets1'}</t>
+          <t>dress2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Prophets1'}</t>
+          <t>Dress2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>party_prophets_choices</t>
+          <t>party_dress_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'prophets2'}</t>
+          <t>dress3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Prophets2'}</t>
+          <t>Dress3</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>party_prophets_choices</t>
+          <t>party_entertainment_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'prophets1'}</t>
+          <t>entertainment1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Prophets1'}</t>
+          <t>Entertainment1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>party_prophets_choices</t>
+          <t>party_entertainment_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'prophets2'}</t>
+          <t>entertainment2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Prophets2'}</t>
+          <t>Entertainment2</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>party_prophets_choices</t>
+          <t>party_entertainment_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>entertainment3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>party_prophets_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>party_prophets_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>party_prophets_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>party_prophets_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>party_prophets_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Entertainment3</t>
         </is>
       </c>
     </row>
